--- a/artfynd/A 31071-2024 artfynd.xlsx
+++ b/artfynd/A 31071-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83572030</v>
+        <v>761689</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Vg</t>
+          <t>Dala, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429017.7899232564</v>
+        <v>429166</v>
       </c>
       <c r="R2" t="n">
-        <v>6457728.409108182</v>
+        <v>6457714</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,36 +738,16 @@
           <t>Dala</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0FE3B4E2-310B-4992-83A8-46DD2D2B70A7</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2011-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>{35532A3B-B085-4DCD-A050-19463A3D4132}</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -786,18 +757,831 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>kultiverad betesmark</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Carin Franson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av särskilt skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>761690</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dala, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>429187</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6457689</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kultiverad betesmark</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Carin Franson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Carin Franson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av särskilt skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83572018</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>429196</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6457683</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>755AD661-77EE-49BF-9A13-DC5004528172</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>{1F070539-6FD4-4793-9260-3E3D2A9855B9}</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Anna Stenström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Anna Stenström, Vikki Bengtsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>83572022</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>429004</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6457777</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>B9AACD16-DFF6-4A47-AB06-EB1E43E01AE9</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>{23BD54E4-FB35-47AF-A7AD-CCDBA2224AA5}</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Vikki Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>83572030</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>429018</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6457728</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0FE3B4E2-310B-4992-83A8-46DD2D2B70A7</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>{35532A3B-B085-4DCD-A050-19463A3D4132}</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Vikki Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>83572086</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>429166</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6457714</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>F1C5E4DA-C8FD-4C6F-977E-B5FD9B291223</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>{7A32D078-E599-4093-A54A-86725D710197}</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Vikki Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>83572099</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>429175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6457699</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>E8F65D11-ADE4-4D0B-A8F2-3F430BCC715C</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>{8B2F287E-D160-46B6-9001-B0BE9B8BE2EE}</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Vikki Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>83572153</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>429187</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6457689</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>F0C421B4-E95A-4CAD-B694-9BA9B58EBAF9</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-06-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>{D55B1E0D-6B96-4FB3-AE26-20CD9C2CF874}</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Vikki Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
